--- a/Tach_ChiPhi_PP_BL.xlsx
+++ b/Tach_ChiPhi_PP_BL.xlsx
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>948924323</v>
+        <v>919245580</v>
       </c>
       <c r="F12" s="39">
         <f>E12*80.79%</f>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>320378418</v>
+        <v>320378409</v>
       </c>
       <c r="F12" s="39">
         <f>E12*80.79%</f>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>78353680</v>
+        <v>78353650</v>
       </c>
       <c r="F14" s="39">
         <f>E14*80.79%</f>
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>672123831</v>
+        <v>672123825</v>
       </c>
       <c r="F14" s="39">
         <f>E14*80.79%</f>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="E15" s="38" t="n">
-        <v>31618876</v>
+        <v>38379584</v>
       </c>
       <c r="F15" s="39">
         <f>E15*80.79%</f>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>64930258</v>
+        <v>64792258</v>
       </c>
       <c r="F16" s="39">
         <f>E16*80.79%</f>

--- a/Tach_ChiPhi_PP_BL.xlsx
+++ b/Tach_ChiPhi_PP_BL.xlsx
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>672123825</v>
+        <v>672123823</v>
       </c>
       <c r="F14" s="39">
         <f>E14*80.79%</f>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="E15" s="38" t="n">
-        <v>38379584</v>
+        <v>38379478</v>
       </c>
       <c r="F15" s="39">
         <f>E15*80.79%</f>

--- a/Tach_ChiPhi_PP_BL.xlsx
+++ b/Tach_ChiPhi_PP_BL.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Times New Roman"/>
       <family val="2"/>
@@ -75,8 +75,21 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <i val="1"/>
+      <color rgb="007B3F00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -89,8 +102,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD580"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFB347"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -216,12 +239,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -346,6 +383,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -991,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.19921875" defaultRowHeight="16.8"/>
   <cols>
     <col width="5.8984375" customWidth="1" style="1" min="1" max="1"/>
@@ -1058,7 +1113,7 @@
         </is>
       </c>
       <c r="C8" s="31">
-        <f>E14</f>
+        <f>E15</f>
         <v/>
       </c>
       <c r="D8" s="23" t="n"/>
@@ -1190,29 +1245,57 @@
       <c r="H13" s="16" t="n"/>
     </row>
     <row r="14" customFormat="1" s="11">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="45" t="n"/>
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
+        </is>
+      </c>
+      <c r="C14" s="46" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="E14" s="47" t="n">
+        <v>-29678743</v>
+      </c>
+      <c r="F14" s="47">
+        <f>E14*80.79%</f>
+        <v/>
+      </c>
+      <c r="G14" s="47">
+        <f>E14-F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="1" s="11">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>Tổng cộng</t>
         </is>
       </c>
-      <c r="B14" s="42" t="n"/>
-      <c r="C14" s="42" t="n"/>
-      <c r="D14" s="43" t="n"/>
-      <c r="E14" s="44">
-        <f>SUM(E12:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="44">
-        <f>SUM(F12:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="44">
-        <f>SUM(G12:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="18" t="n"/>
-    </row>
-    <row r="15" customFormat="1" s="11"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="43" t="n"/>
+      <c r="E15" s="44">
+        <f>SUM(E12:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="44">
+        <f>SUM(F12:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="44">
+        <f>SUM(G12:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="18" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="D10:D11"/>
@@ -1221,11 +1304,11 @@
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1237,7 +1320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.19921875" defaultRowHeight="16.8"/>
   <cols>
     <col width="5.8984375" customWidth="1" style="1" min="1" max="1"/>
@@ -1304,7 +1387,7 @@
         </is>
       </c>
       <c r="C8" s="31">
-        <f>E14</f>
+        <f>E15</f>
         <v/>
       </c>
       <c r="D8" s="23" t="n"/>
@@ -1436,29 +1519,57 @@
       <c r="H13" s="16" t="n"/>
     </row>
     <row r="14" customFormat="1" s="11">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="45" t="n"/>
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
+        </is>
+      </c>
+      <c r="C14" s="46" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="E14" s="47" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F14" s="47">
+        <f>E14*80.79%</f>
+        <v/>
+      </c>
+      <c r="G14" s="47">
+        <f>E14-F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="1" s="11">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>Tổng cộng</t>
         </is>
       </c>
-      <c r="B14" s="42" t="n"/>
-      <c r="C14" s="42" t="n"/>
-      <c r="D14" s="43" t="n"/>
-      <c r="E14" s="44">
-        <f>SUM(E12:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="44">
-        <f>SUM(F12:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="44">
-        <f>SUM(G12:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="18" t="n"/>
-    </row>
-    <row r="15" customFormat="1" s="11"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="43" t="n"/>
+      <c r="E15" s="44">
+        <f>SUM(E12:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="44">
+        <f>SUM(F12:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="44">
+        <f>SUM(G12:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="18" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="D10:D11"/>
@@ -1467,11 +1578,11 @@
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1483,7 +1594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.19921875" defaultRowHeight="16.8"/>
   <cols>
     <col width="5.8984375" customWidth="1" style="1" min="1" max="1"/>
@@ -1550,7 +1661,7 @@
         </is>
       </c>
       <c r="C8" s="31">
-        <f>E18</f>
+        <f>E19</f>
         <v/>
       </c>
       <c r="D8" s="23" t="n"/>
@@ -1740,52 +1851,55 @@
       <c r="H15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n">
+      <c r="A16" s="45" t="n"/>
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="D16" s="46" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="E16" s="47" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F16" s="47">
+        <f>E16*80.79%</f>
+        <v/>
+      </c>
+      <c r="G16" s="47">
+        <f>E16-F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>VTAD2606002 - Sửa chữa lớn FCO, LA năm 2026</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>VTAD2606002</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="E16" s="38" t="n">
+      <c r="E17" s="38" t="n">
         <v>172480327</v>
-      </c>
-      <c r="F16" s="39">
-        <f>E16*80.79%</f>
-        <v/>
-      </c>
-      <c r="G16" s="39">
-        <f>E16-F16</f>
-        <v/>
-      </c>
-      <c r="H16" s="20" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="40" t="n"/>
-      <c r="B17" s="40" t="n"/>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>VTAD2606002</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>Hạ thế</t>
-        </is>
-      </c>
-      <c r="E17" s="38" t="n">
-        <v>0</v>
       </c>
       <c r="F17" s="39">
         <f>E17*80.79%</f>
@@ -1795,43 +1909,69 @@
         <f>E17-F17</f>
         <v/>
       </c>
-      <c r="H17" s="16" t="n"/>
+      <c r="H17" s="20" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="41" t="inlineStr">
+      <c r="A18" s="40" t="n"/>
+      <c r="B18" s="40" t="n"/>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="39">
+        <f>E18*80.79%</f>
+        <v/>
+      </c>
+      <c r="G18" s="39">
+        <f>E18-F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="16" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="41" t="inlineStr">
         <is>
           <t>Tổng cộng</t>
         </is>
       </c>
-      <c r="B18" s="42" t="n"/>
-      <c r="C18" s="42" t="n"/>
-      <c r="D18" s="43" t="n"/>
-      <c r="E18" s="44">
-        <f>SUM(E12:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="44">
-        <f>SUM(F12:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="44">
-        <f>SUM(G12:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="18" t="n"/>
+      <c r="B19" s="42" t="n"/>
+      <c r="C19" s="42" t="n"/>
+      <c r="D19" s="43" t="n"/>
+      <c r="E19" s="44">
+        <f>SUM(E12:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="44">
+        <f>SUM(F12:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="44">
+        <f>SUM(G12:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A18:D18"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B17:B18"/>
     <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>
@@ -1848,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.19921875" defaultRowHeight="16.8"/>
   <cols>
     <col width="5.8984375" customWidth="1" style="1" min="1" max="1"/>
@@ -1915,7 +2055,7 @@
         </is>
       </c>
       <c r="C8" s="31">
-        <f>E18</f>
+        <f>E21</f>
         <v/>
       </c>
       <c r="D8" s="23" t="n"/>
@@ -2008,7 +2148,7 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>47715337</v>
+        <v>69891202</v>
       </c>
       <c r="F12" s="39">
         <f>E12*80.79%</f>
@@ -2034,7 +2174,7 @@
         </is>
       </c>
       <c r="E13" s="38" t="n">
-        <v>242564761</v>
+        <v>220388896</v>
       </c>
       <c r="F13" s="39">
         <f>E13*80.79%</f>
@@ -2105,98 +2245,181 @@
       <c r="H15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n">
+      <c r="A16" s="45" t="n"/>
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="D16" s="46" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="E16" s="47" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F16" s="47">
+        <f>E16*80.79%</f>
+        <v/>
+      </c>
+      <c r="G16" s="47">
+        <f>E16-F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="n"/>
+      <c r="B17" s="48" t="n"/>
+      <c r="C17" s="49" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="D17" s="49" t="inlineStr">
+        <is>
+          <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="E17" s="50" t="n">
+        <v>-106</v>
+      </c>
+      <c r="F17" s="50">
+        <f>E17*80.79%</f>
+        <v/>
+      </c>
+      <c r="G17" s="50">
+        <f>E17-F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>VTAD2606002 - Sửa chữa lớn FCO, LA năm 2026</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>VTAD2606002</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="E16" s="38" t="n">
+      <c r="E18" s="38" t="n">
         <v>64792258</v>
       </c>
-      <c r="F16" s="39">
-        <f>E16*80.79%</f>
-        <v/>
-      </c>
-      <c r="G16" s="39">
-        <f>E16-F16</f>
-        <v/>
-      </c>
-      <c r="H16" s="20" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="40" t="n"/>
-      <c r="B17" s="40" t="n"/>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="F18" s="39">
+        <f>E18*80.79%</f>
+        <v/>
+      </c>
+      <c r="G18" s="39">
+        <f>E18-F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="20" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="40" t="n"/>
+      <c r="B19" s="40" t="n"/>
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>VTAD2606002</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="E17" s="38" t="n">
+      <c r="E19" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="39">
-        <f>E17*80.79%</f>
-        <v/>
-      </c>
-      <c r="G17" s="39">
-        <f>E17-F17</f>
-        <v/>
-      </c>
-      <c r="H17" s="16" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="41" t="inlineStr">
+      <c r="F19" s="39">
+        <f>E19*80.79%</f>
+        <v/>
+      </c>
+      <c r="G19" s="39">
+        <f>E19-F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="16" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="n"/>
+      <c r="B20" s="45" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
+        </is>
+      </c>
+      <c r="C20" s="46" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="D20" s="46" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="E20" s="47" t="n">
+        <v>-138000</v>
+      </c>
+      <c r="F20" s="47">
+        <f>E20*80.79%</f>
+        <v/>
+      </c>
+      <c r="G20" s="47">
+        <f>E20-F20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>Tổng cộng</t>
         </is>
       </c>
-      <c r="B18" s="42" t="n"/>
-      <c r="C18" s="42" t="n"/>
-      <c r="D18" s="43" t="n"/>
-      <c r="E18" s="44">
-        <f>SUM(E12:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="44">
-        <f>SUM(F12:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="44">
-        <f>SUM(G12:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="18" t="n"/>
+      <c r="B21" s="42" t="n"/>
+      <c r="C21" s="42" t="n"/>
+      <c r="D21" s="43" t="n"/>
+      <c r="E21" s="44">
+        <f>SUM(E12:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="44">
+        <f>SUM(F12:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="44">
+        <f>SUM(G12:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A18:D18"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A18:A19"/>
     <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>

--- a/Tach_ChiPhi_PP_BL.xlsx
+++ b/Tach_ChiPhi_PP_BL.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="Times New Roman"/>
       <family val="2"/>
@@ -75,21 +75,8 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Times New Roman"/>
-      <i val="1"/>
-      <color rgb="007B3F00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color rgb="00C0392B"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -102,18 +89,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD580"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFB347"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -239,26 +216,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -383,24 +346,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1046,7 +991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.19921875" defaultRowHeight="16.8"/>
   <cols>
     <col width="5.8984375" customWidth="1" style="1" min="1" max="1"/>
@@ -1113,7 +1058,7 @@
         </is>
       </c>
       <c r="C8" s="31">
-        <f>E15</f>
+        <f>E14</f>
         <v/>
       </c>
       <c r="D8" s="23" t="n"/>
@@ -1245,57 +1190,29 @@
       <c r="H13" s="16" t="n"/>
     </row>
     <row r="14" customFormat="1" s="11">
-      <c r="A14" s="45" t="n"/>
-      <c r="B14" s="45" t="inlineStr">
-        <is>
-          <t>Thu hồi VTTB</t>
-        </is>
-      </c>
-      <c r="C14" s="46" t="inlineStr">
-        <is>
-          <t>VTAD2606001</t>
-        </is>
-      </c>
-      <c r="D14" s="46" t="inlineStr">
-        <is>
-          <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="E14" s="47" t="n">
-        <v>-29678743</v>
-      </c>
-      <c r="F14" s="47">
-        <f>E14*80.79%</f>
-        <v/>
-      </c>
-      <c r="G14" s="47">
-        <f>E14-F14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="1" s="11">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>Tổng cộng</t>
         </is>
       </c>
-      <c r="B15" s="42" t="n"/>
-      <c r="C15" s="42" t="n"/>
-      <c r="D15" s="43" t="n"/>
-      <c r="E15" s="44">
-        <f>SUM(E12:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="44">
-        <f>SUM(F12:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="44">
-        <f>SUM(G12:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="18" t="n"/>
-    </row>
+      <c r="B14" s="42" t="n"/>
+      <c r="C14" s="42" t="n"/>
+      <c r="D14" s="43" t="n"/>
+      <c r="E14" s="44">
+        <f>SUM(E12:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="44">
+        <f>SUM(F12:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="44">
+        <f>SUM(G12:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="18" t="n"/>
+    </row>
+    <row r="15" customFormat="1" s="11"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="D10:D11"/>
@@ -1304,11 +1221,11 @@
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A15:D15"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1320,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.19921875" defaultRowHeight="16.8"/>
   <cols>
     <col width="5.8984375" customWidth="1" style="1" min="1" max="1"/>
@@ -1387,7 +1304,7 @@
         </is>
       </c>
       <c r="C8" s="31">
-        <f>E15</f>
+        <f>E14</f>
         <v/>
       </c>
       <c r="D8" s="23" t="n"/>
@@ -1519,57 +1436,29 @@
       <c r="H13" s="16" t="n"/>
     </row>
     <row r="14" customFormat="1" s="11">
-      <c r="A14" s="45" t="n"/>
-      <c r="B14" s="45" t="inlineStr">
-        <is>
-          <t>Thu hồi VTTB</t>
-        </is>
-      </c>
-      <c r="C14" s="46" t="inlineStr">
-        <is>
-          <t>VTAD2606001</t>
-        </is>
-      </c>
-      <c r="D14" s="46" t="inlineStr">
-        <is>
-          <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="E14" s="47" t="n">
-        <v>-9</v>
-      </c>
-      <c r="F14" s="47">
-        <f>E14*80.79%</f>
-        <v/>
-      </c>
-      <c r="G14" s="47">
-        <f>E14-F14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="1" s="11">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>Tổng cộng</t>
         </is>
       </c>
-      <c r="B15" s="42" t="n"/>
-      <c r="C15" s="42" t="n"/>
-      <c r="D15" s="43" t="n"/>
-      <c r="E15" s="44">
-        <f>SUM(E12:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="44">
-        <f>SUM(F12:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="44">
-        <f>SUM(G12:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="18" t="n"/>
-    </row>
+      <c r="B14" s="42" t="n"/>
+      <c r="C14" s="42" t="n"/>
+      <c r="D14" s="43" t="n"/>
+      <c r="E14" s="44">
+        <f>SUM(E12:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="44">
+        <f>SUM(F12:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="44">
+        <f>SUM(G12:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="18" t="n"/>
+    </row>
+    <row r="15" customFormat="1" s="11"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="D10:D11"/>
@@ -1578,11 +1467,11 @@
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A15:D15"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1594,7 +1483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.19921875" defaultRowHeight="16.8"/>
   <cols>
     <col width="5.8984375" customWidth="1" style="1" min="1" max="1"/>
@@ -1661,7 +1550,7 @@
         </is>
       </c>
       <c r="C8" s="31">
-        <f>E19</f>
+        <f>E18</f>
         <v/>
       </c>
       <c r="D8" s="23" t="n"/>
@@ -1851,43 +1740,40 @@
       <c r="H15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="n"/>
-      <c r="B16" s="45" t="inlineStr">
-        <is>
-          <t>Thu hồi VTTB</t>
-        </is>
-      </c>
-      <c r="C16" s="46" t="inlineStr">
-        <is>
-          <t>VTAD2606001</t>
-        </is>
-      </c>
-      <c r="D16" s="46" t="inlineStr">
+      <c r="A16" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>VTAD2606002 - Sửa chữa lớn FCO, LA năm 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="E16" s="47" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F16" s="47">
+      <c r="E16" s="38" t="n">
+        <v>172480327</v>
+      </c>
+      <c r="F16" s="39">
         <f>E16*80.79%</f>
         <v/>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="39">
         <f>E16-F16</f>
         <v/>
       </c>
+      <c r="H16" s="20" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="37" t="inlineStr">
-        <is>
-          <t>VTAD2606002 - Sửa chữa lớn FCO, LA năm 2026</t>
-        </is>
-      </c>
+      <c r="A17" s="40" t="n"/>
+      <c r="B17" s="40" t="n"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
           <t>VTAD2606002</t>
@@ -1895,11 +1781,11 @@
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Trung thế</t>
+          <t>Hạ thế</t>
         </is>
       </c>
       <c r="E17" s="38" t="n">
-        <v>172480327</v>
+        <v>0</v>
       </c>
       <c r="F17" s="39">
         <f>E17*80.79%</f>
@@ -1909,69 +1795,43 @@
         <f>E17-F17</f>
         <v/>
       </c>
-      <c r="H17" s="20" t="n"/>
+      <c r="H17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="n"/>
-      <c r="B18" s="40" t="n"/>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>VTAD2606002</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>Hạ thế</t>
-        </is>
-      </c>
-      <c r="E18" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="39">
-        <f>E18*80.79%</f>
-        <v/>
-      </c>
-      <c r="G18" s="39">
-        <f>E18-F18</f>
-        <v/>
-      </c>
-      <c r="H18" s="16" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="41" t="inlineStr">
+      <c r="A18" s="41" t="inlineStr">
         <is>
           <t>Tổng cộng</t>
         </is>
       </c>
-      <c r="B19" s="42" t="n"/>
-      <c r="C19" s="42" t="n"/>
-      <c r="D19" s="43" t="n"/>
-      <c r="E19" s="44">
-        <f>SUM(E12:E18)</f>
-        <v/>
-      </c>
-      <c r="F19" s="44">
-        <f>SUM(F12:F18)</f>
-        <v/>
-      </c>
-      <c r="G19" s="44">
-        <f>SUM(G12:G18)</f>
-        <v/>
-      </c>
-      <c r="H19" s="18" t="n"/>
+      <c r="B18" s="42" t="n"/>
+      <c r="C18" s="42" t="n"/>
+      <c r="D18" s="43" t="n"/>
+      <c r="E18" s="44">
+        <f>SUM(E12:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="44">
+        <f>SUM(F12:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="44">
+        <f>SUM(G12:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B17:B18"/>
     <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>
@@ -1988,7 +1848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.19921875" defaultRowHeight="16.8"/>
   <cols>
     <col width="5.8984375" customWidth="1" style="1" min="1" max="1"/>
@@ -2055,7 +1915,7 @@
         </is>
       </c>
       <c r="C8" s="31">
-        <f>E21</f>
+        <f>E18</f>
         <v/>
       </c>
       <c r="D8" s="23" t="n"/>
@@ -2148,7 +2008,7 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>69891202</v>
+        <v>47715337</v>
       </c>
       <c r="F12" s="39">
         <f>E12*80.79%</f>
@@ -2174,7 +2034,7 @@
         </is>
       </c>
       <c r="E13" s="38" t="n">
-        <v>220388896</v>
+        <v>242564761</v>
       </c>
       <c r="F13" s="39">
         <f>E13*80.79%</f>
@@ -2245,181 +2105,98 @@
       <c r="H15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="n"/>
-      <c r="B16" s="45" t="inlineStr">
-        <is>
-          <t>Thu hồi VTTB</t>
-        </is>
-      </c>
-      <c r="C16" s="46" t="inlineStr">
-        <is>
-          <t>VTAD2606001</t>
-        </is>
-      </c>
-      <c r="D16" s="46" t="inlineStr">
+      <c r="A16" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>VTAD2606002 - Sửa chữa lớn FCO, LA năm 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="E16" s="47" t="n">
-        <v>-8</v>
-      </c>
-      <c r="F16" s="47">
+      <c r="E16" s="38" t="n">
+        <v>64792258</v>
+      </c>
+      <c r="F16" s="39">
         <f>E16*80.79%</f>
         <v/>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="39">
         <f>E16-F16</f>
         <v/>
       </c>
+      <c r="H16" s="20" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="n"/>
-      <c r="B17" s="48" t="n"/>
-      <c r="C17" s="49" t="inlineStr">
-        <is>
-          <t>VTAD2606001</t>
-        </is>
-      </c>
-      <c r="D17" s="49" t="inlineStr">
+      <c r="A17" s="40" t="n"/>
+      <c r="B17" s="40" t="n"/>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="E17" s="50" t="n">
-        <v>-106</v>
-      </c>
-      <c r="F17" s="50">
+      <c r="E17" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="39">
         <f>E17*80.79%</f>
         <v/>
       </c>
-      <c r="G17" s="50">
+      <c r="G17" s="39">
         <f>E17-F17</f>
         <v/>
       </c>
+      <c r="H17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>VTAD2606002 - Sửa chữa lớn FCO, LA năm 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>VTAD2606002</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="E18" s="38" t="n">
-        <v>64792258</v>
-      </c>
-      <c r="F18" s="39">
-        <f>E18*80.79%</f>
-        <v/>
-      </c>
-      <c r="G18" s="39">
-        <f>E18-F18</f>
-        <v/>
-      </c>
-      <c r="H18" s="20" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="40" t="n"/>
-      <c r="B19" s="40" t="n"/>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>VTAD2606002</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>Hạ thế</t>
-        </is>
-      </c>
-      <c r="E19" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="39">
-        <f>E19*80.79%</f>
-        <v/>
-      </c>
-      <c r="G19" s="39">
-        <f>E19-F19</f>
-        <v/>
-      </c>
-      <c r="H19" s="16" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="45" t="n"/>
-      <c r="B20" s="45" t="inlineStr">
-        <is>
-          <t>Thu hồi VTTB</t>
-        </is>
-      </c>
-      <c r="C20" s="46" t="inlineStr">
-        <is>
-          <t>VTAD2606002</t>
-        </is>
-      </c>
-      <c r="D20" s="46" t="inlineStr">
-        <is>
-          <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="E20" s="47" t="n">
-        <v>-138000</v>
-      </c>
-      <c r="F20" s="47">
-        <f>E20*80.79%</f>
-        <v/>
-      </c>
-      <c r="G20" s="47">
-        <f>E20-F20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="41" t="inlineStr">
+      <c r="A18" s="41" t="inlineStr">
         <is>
           <t>Tổng cộng</t>
         </is>
       </c>
-      <c r="B21" s="42" t="n"/>
-      <c r="C21" s="42" t="n"/>
-      <c r="D21" s="43" t="n"/>
-      <c r="E21" s="44">
-        <f>SUM(E12:E20)</f>
-        <v/>
-      </c>
-      <c r="F21" s="44">
-        <f>SUM(F12:F20)</f>
-        <v/>
-      </c>
-      <c r="G21" s="44">
-        <f>SUM(G12:G20)</f>
-        <v/>
-      </c>
-      <c r="H21" s="18" t="n"/>
+      <c r="B18" s="42" t="n"/>
+      <c r="C18" s="42" t="n"/>
+      <c r="D18" s="43" t="n"/>
+      <c r="E18" s="44">
+        <f>SUM(E12:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="44">
+        <f>SUM(F12:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="44">
+        <f>SUM(G12:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B18:B19"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
     <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>

--- a/Tach_ChiPhi_PP_BL.xlsx
+++ b/Tach_ChiPhi_PP_BL.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 4" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 6" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -991,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.19921875" defaultRowHeight="16.8"/>
   <cols>
     <col width="5.8984375" customWidth="1" style="1" min="1" max="1"/>
@@ -1058,7 +1059,7 @@
         </is>
       </c>
       <c r="C8" s="31">
-        <f>E14</f>
+        <f>E15</f>
         <v/>
       </c>
       <c r="D8" s="23" t="n"/>
@@ -1190,42 +1191,67 @@
       <c r="H13" s="16" t="n"/>
     </row>
     <row r="14" customFormat="1" s="11">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="40" t="n"/>
+      <c r="B14" s="40" t="n"/>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>Hoàn nhập - Trung thế</t>
+        </is>
+      </c>
+      <c r="E14" s="38" t="n">
+        <v>-29678743</v>
+      </c>
+      <c r="F14" s="39">
+        <f>E14*80.79%</f>
+        <v/>
+      </c>
+      <c r="G14" s="39">
+        <f>E14-F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="16" t="n"/>
+    </row>
+    <row r="15" customFormat="1" s="11">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>Tổng cộng</t>
         </is>
       </c>
-      <c r="B14" s="42" t="n"/>
-      <c r="C14" s="42" t="n"/>
-      <c r="D14" s="43" t="n"/>
-      <c r="E14" s="44">
-        <f>SUM(E12:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="44">
-        <f>SUM(F12:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="44">
-        <f>SUM(G12:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="18" t="n"/>
-    </row>
-    <row r="15" customFormat="1" s="11"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="43" t="n"/>
+      <c r="E15" s="44">
+        <f>SUM(E12:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="44">
+        <f>SUM(F12:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="44">
+        <f>SUM(G12:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="18" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A12:A14"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B14"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1237,7 +1263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.19921875" defaultRowHeight="16.8"/>
   <cols>
     <col width="5.8984375" customWidth="1" style="1" min="1" max="1"/>
@@ -1304,7 +1330,7 @@
         </is>
       </c>
       <c r="C8" s="31">
-        <f>E14</f>
+        <f>E15</f>
         <v/>
       </c>
       <c r="D8" s="23" t="n"/>
@@ -1436,42 +1462,67 @@
       <c r="H13" s="16" t="n"/>
     </row>
     <row r="14" customFormat="1" s="11">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="40" t="n"/>
+      <c r="B14" s="40" t="n"/>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>Hoàn nhập - Trung thế</t>
+        </is>
+      </c>
+      <c r="E14" s="38" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F14" s="39">
+        <f>E14*80.79%</f>
+        <v/>
+      </c>
+      <c r="G14" s="39">
+        <f>E14-F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="16" t="n"/>
+    </row>
+    <row r="15" customFormat="1" s="11">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>Tổng cộng</t>
         </is>
       </c>
-      <c r="B14" s="42" t="n"/>
-      <c r="C14" s="42" t="n"/>
-      <c r="D14" s="43" t="n"/>
-      <c r="E14" s="44">
-        <f>SUM(E12:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="44">
-        <f>SUM(F12:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="44">
-        <f>SUM(G12:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="18" t="n"/>
-    </row>
-    <row r="15" customFormat="1" s="11"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="43" t="n"/>
+      <c r="E15" s="44">
+        <f>SUM(E12:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="44">
+        <f>SUM(F12:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="44">
+        <f>SUM(G12:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="18" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A12:A14"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B14"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1483,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.19921875" defaultRowHeight="16.8"/>
   <cols>
     <col width="5.8984375" customWidth="1" style="1" min="1" max="1"/>
@@ -1550,7 +1601,7 @@
         </is>
       </c>
       <c r="C8" s="31">
-        <f>E18</f>
+        <f>E19</f>
         <v/>
       </c>
       <c r="D8" s="23" t="n"/>
@@ -1740,26 +1791,20 @@
       <c r="H15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>VTAD2606002 - Sửa chữa lớn FCO, LA năm 2026</t>
-        </is>
-      </c>
+      <c r="A16" s="40" t="n"/>
+      <c r="B16" s="40" t="n"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2606001</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Trung thế</t>
+          <t>Hoàn nhập - Chưa phân loại</t>
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>172480327</v>
+        <v>-30</v>
       </c>
       <c r="F16" s="39">
         <f>E16*80.79%</f>
@@ -1769,11 +1814,17 @@
         <f>E16-F16</f>
         <v/>
       </c>
-      <c r="H16" s="20" t="n"/>
+      <c r="H16" s="16" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="n"/>
-      <c r="B17" s="40" t="n"/>
+      <c r="A17" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>VTAD2606002 - Sửa chữa lớn FCO, LA năm 2026</t>
+        </is>
+      </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
           <t>VTAD2606002</t>
@@ -1781,11 +1832,11 @@
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Hạ thế</t>
+          <t>Trung thế</t>
         </is>
       </c>
       <c r="E17" s="38" t="n">
-        <v>0</v>
+        <v>172480327</v>
       </c>
       <c r="F17" s="39">
         <f>E17*80.79%</f>
@@ -1795,48 +1846,74 @@
         <f>E17-F17</f>
         <v/>
       </c>
-      <c r="H17" s="16" t="n"/>
+      <c r="H17" s="20" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="41" t="inlineStr">
+      <c r="A18" s="40" t="n"/>
+      <c r="B18" s="40" t="n"/>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="39">
+        <f>E18*80.79%</f>
+        <v/>
+      </c>
+      <c r="G18" s="39">
+        <f>E18-F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="16" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="41" t="inlineStr">
         <is>
           <t>Tổng cộng</t>
         </is>
       </c>
-      <c r="B18" s="42" t="n"/>
-      <c r="C18" s="42" t="n"/>
-      <c r="D18" s="43" t="n"/>
-      <c r="E18" s="44">
-        <f>SUM(E12:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="44">
-        <f>SUM(F12:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="44">
-        <f>SUM(G12:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="18" t="n"/>
+      <c r="B19" s="42" t="n"/>
+      <c r="C19" s="42" t="n"/>
+      <c r="D19" s="43" t="n"/>
+      <c r="E19" s="44">
+        <f>SUM(E12:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="44">
+        <f>SUM(F12:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="44">
+        <f>SUM(G12:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A18:D18"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A14:A16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1848,7 +1925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.19921875" defaultRowHeight="16.8"/>
   <cols>
     <col width="5.8984375" customWidth="1" style="1" min="1" max="1"/>
@@ -1915,7 +1992,7 @@
         </is>
       </c>
       <c r="C8" s="31">
-        <f>E18</f>
+        <f>E21</f>
         <v/>
       </c>
       <c r="D8" s="23" t="n"/>
@@ -2066,7 +2143,7 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>672123823</v>
+        <v>689684187</v>
       </c>
       <c r="F14" s="39">
         <f>E14*80.79%</f>
@@ -2105,26 +2182,20 @@
       <c r="H15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>VTAD2606002 - Sửa chữa lớn FCO, LA năm 2026</t>
-        </is>
-      </c>
+      <c r="A16" s="40" t="n"/>
+      <c r="B16" s="40" t="n"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2606001</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Trung thế</t>
+          <t>Hoàn nhập - Trung thế</t>
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>64792258</v>
+        <v>-6</v>
       </c>
       <c r="F16" s="39">
         <f>E16*80.79%</f>
@@ -2134,23 +2205,23 @@
         <f>E16-F16</f>
         <v/>
       </c>
-      <c r="H16" s="20" t="n"/>
+      <c r="H16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="40" t="n"/>
       <c r="B17" s="40" t="n"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>VTAD2606002</t>
+          <t>VTAD2606001</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Hạ thế</t>
+          <t>Hoàn nhập - Chưa phân loại</t>
         </is>
       </c>
       <c r="E17" s="38" t="n">
-        <v>0</v>
+        <v>-108</v>
       </c>
       <c r="F17" s="39">
         <f>E17*80.79%</f>
@@ -2163,45 +2234,400 @@
       <c r="H17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="41" t="inlineStr">
+      <c r="A18" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>VTAD2606002 - Sửa chữa lớn FCO, LA năm 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>64792258</v>
+      </c>
+      <c r="F18" s="39">
+        <f>E18*80.79%</f>
+        <v/>
+      </c>
+      <c r="G18" s="39">
+        <f>E18-F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="20" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="40" t="n"/>
+      <c r="B19" s="40" t="n"/>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="E19" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="39">
+        <f>E19*80.79%</f>
+        <v/>
+      </c>
+      <c r="G19" s="39">
+        <f>E19-F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="16" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="n"/>
+      <c r="B20" s="40" t="n"/>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>Hoàn nhập - Chưa phân loại</t>
+        </is>
+      </c>
+      <c r="E20" s="38" t="n">
+        <v>-138000</v>
+      </c>
+      <c r="F20" s="39">
+        <f>E20*80.79%</f>
+        <v/>
+      </c>
+      <c r="G20" s="39">
+        <f>E20-F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="16" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>Tổng cộng</t>
         </is>
       </c>
-      <c r="B18" s="42" t="n"/>
-      <c r="C18" s="42" t="n"/>
-      <c r="D18" s="43" t="n"/>
-      <c r="E18" s="44">
-        <f>SUM(E12:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="44">
-        <f>SUM(F12:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="44">
-        <f>SUM(G12:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="18" t="n"/>
+      <c r="B21" s="42" t="n"/>
+      <c r="C21" s="42" t="n"/>
+      <c r="D21" s="43" t="n"/>
+      <c r="E21" s="44">
+        <f>SUM(E12:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="44">
+        <f>SUM(F12:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="44">
+        <f>SUM(G12:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A14:A17"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A18:A20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.19921875" defaultRowHeight="16.8"/>
+  <cols>
+    <col width="5.8984375" customWidth="1" style="1" min="1" max="1"/>
+    <col width="34.19921875" customWidth="1" style="1" min="2" max="2"/>
+    <col width="15.59765625" customWidth="1" style="1" min="3" max="4"/>
+    <col width="13.296875" bestFit="1" customWidth="1" style="9" min="5" max="5"/>
+    <col width="23.69921875" bestFit="1" customWidth="1" style="4" min="6" max="6"/>
+    <col width="24.19921875" customWidth="1" style="4" min="7" max="7"/>
+    <col width="15.8984375" customWidth="1" style="1" min="8" max="8"/>
+    <col width="15.3984375" customWidth="1" style="11" min="9" max="9"/>
+    <col width="21.296875" bestFit="1" customWidth="1" style="1" min="10" max="10"/>
+    <col width="8.19921875" customWidth="1" style="1" min="11" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.6" customHeight="1">
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>TÁCH CHI PHÍ SCL - KHÂU BÁN LẺ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>Căn cứ công văn 3379/EVNHCMC-TCKT ngày 14/8/2025 V/v tỷ lệ phân bổ chi phí dùng chung khâu phân phối và khâu kinh doanh bán lẻ điện áp dụng 6TCN 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19.2" customHeight="1">
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>GL_............ ngày     /   06   /2026</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n"/>
+    </row>
+    <row r="6" ht="19.2" customHeight="1">
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Tổng số tiền trước thuế:</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="19.2" customHeight="1">
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>Thuế GTGT:</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="19.2" customHeight="1">
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Tổng tiền thanh toán:</t>
+        </is>
+      </c>
+      <c r="C8" s="31">
+        <f>E15</f>
+        <v/>
+      </c>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="I9" s="11" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>Tên công trình</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Mã CT</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Trung-Hạ thế</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Tổng CP</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Khâu phân phối (80.79%)</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Khâu bán lẻ 19.21%</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>TK: 627611-1310-610</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>TK: 627611-1320-610</t>
+        </is>
+      </c>
+      <c r="H11" s="35" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>VTAD2606001 - Sửa chữa lớn TSCĐ hệ thống đo đếm trên địa bàn Công ty Điện Lực Vũng Tàu năm 2026 - Phần bảo trì TU, TI</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="E12" s="38" t="n">
+        <v>33539989</v>
+      </c>
+      <c r="F12" s="39">
+        <f>E12*80.79%</f>
+        <v/>
+      </c>
+      <c r="G12" s="39">
+        <f>E12-F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="20" t="n"/>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="40" t="n"/>
+      <c r="B13" s="40" t="n"/>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="E13" s="38" t="n">
+        <v>30794511</v>
+      </c>
+      <c r="F13" s="39">
+        <f>E13*80.79%</f>
+        <v/>
+      </c>
+      <c r="G13" s="39">
+        <f>E13-F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="16" t="n"/>
+    </row>
+    <row r="14" customFormat="1" s="11">
+      <c r="A14" s="40" t="n"/>
+      <c r="B14" s="40" t="n"/>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>Hoàn nhập - Chưa phân loại</t>
+        </is>
+      </c>
+      <c r="E14" s="38" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F14" s="39">
+        <f>E14*80.79%</f>
+        <v/>
+      </c>
+      <c r="G14" s="39">
+        <f>E14-F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="16" t="n"/>
+    </row>
+    <row r="15" customFormat="1" s="11">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="43" t="n"/>
+      <c r="E15" s="44">
+        <f>SUM(E12:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="44">
+        <f>SUM(F12:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="44">
+        <f>SUM(G12:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="H10:H11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tach_ChiPhi_PP_BL.xlsx
+++ b/Tach_ChiPhi_PP_BL.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 4" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 5" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 6" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 7" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1423,7 +1424,7 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>320378409</v>
+        <v>320378418</v>
       </c>
       <c r="F12" s="39">
         <f>E12*80.79%</f>
@@ -1752,7 +1753,7 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>78353650</v>
+        <v>78353679</v>
       </c>
       <c r="F14" s="39">
         <f>E14*80.79%</f>
@@ -2143,7 +2144,7 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>689684187</v>
+        <v>689684195</v>
       </c>
       <c r="F14" s="39">
         <f>E14*80.79%</f>
@@ -2169,7 +2170,7 @@
         </is>
       </c>
       <c r="E15" s="38" t="n">
-        <v>38379478</v>
+        <v>38379584</v>
       </c>
       <c r="F15" s="39">
         <f>E15*80.79%</f>
@@ -2528,7 +2529,7 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>33539989</v>
+        <v>33540001</v>
       </c>
       <c r="F12" s="39">
         <f>E12*80.79%</f>
@@ -2554,7 +2555,7 @@
         </is>
       </c>
       <c r="E13" s="38" t="n">
-        <v>30794511</v>
+        <v>30794618</v>
       </c>
       <c r="F13" s="39">
         <f>E13*80.79%</f>
@@ -2580,7 +2581,7 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>-12</v>
+        <v>-119</v>
       </c>
       <c r="F14" s="39">
         <f>E14*80.79%</f>
@@ -2631,4 +2632,447 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.19921875" defaultRowHeight="16.8"/>
+  <cols>
+    <col width="5.8984375" customWidth="1" style="1" min="1" max="1"/>
+    <col width="34.19921875" customWidth="1" style="1" min="2" max="2"/>
+    <col width="15.59765625" customWidth="1" style="1" min="3" max="4"/>
+    <col width="13.296875" bestFit="1" customWidth="1" style="9" min="5" max="5"/>
+    <col width="23.69921875" bestFit="1" customWidth="1" style="4" min="6" max="6"/>
+    <col width="24.19921875" customWidth="1" style="4" min="7" max="7"/>
+    <col width="15.8984375" customWidth="1" style="1" min="8" max="8"/>
+    <col width="15.3984375" customWidth="1" style="11" min="9" max="9"/>
+    <col width="21.296875" bestFit="1" customWidth="1" style="1" min="10" max="10"/>
+    <col width="8.19921875" customWidth="1" style="1" min="11" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.6" customHeight="1">
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>TÁCH CHI PHÍ SCL - KHÂU BÁN LẺ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>Căn cứ công văn 3379/EVNHCMC-TCKT ngày 14/8/2025 V/v tỷ lệ phân bổ chi phí dùng chung khâu phân phối và khâu kinh doanh bán lẻ điện áp dụng 6TCN 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19.2" customHeight="1">
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>GL_............ ngày     /   07   /2026</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n"/>
+    </row>
+    <row r="6" ht="19.2" customHeight="1">
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Tổng số tiền trước thuế:</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="19.2" customHeight="1">
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>Thuế GTGT:</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="19.2" customHeight="1">
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Tổng tiền thanh toán:</t>
+        </is>
+      </c>
+      <c r="C8" s="31">
+        <f>E21</f>
+        <v/>
+      </c>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="I9" s="11" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>Tên công trình</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Mã CT</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Trung-Hạ thế</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Tổng CP</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Khâu phân phối (80.79%)</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Khâu bán lẻ 19.21%</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>TK: 627611-1310-610</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>TK: 627611-1320-610</t>
+        </is>
+      </c>
+      <c r="H11" s="35" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>VTAD2606001 - Sửa chữa lớn TSCĐ hệ thống đo đếm trên địa bàn Công ty Điện Lực Vũng Tàu năm 2026 - Phần bảo trì TU, TI</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="E12" s="38" t="n">
+        <v>886544244</v>
+      </c>
+      <c r="F12" s="39">
+        <f>E12*80.79%</f>
+        <v/>
+      </c>
+      <c r="G12" s="39">
+        <f>E12-F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="20" t="n"/>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="40" t="n"/>
+      <c r="B13" s="40" t="n"/>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="E13" s="38" t="n">
+        <v>16388489</v>
+      </c>
+      <c r="F13" s="39">
+        <f>E13*80.79%</f>
+        <v/>
+      </c>
+      <c r="G13" s="39">
+        <f>E13-F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="16" t="n"/>
+    </row>
+    <row r="14" customFormat="1" s="11">
+      <c r="A14" s="40" t="n"/>
+      <c r="B14" s="40" t="n"/>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>Hoàn nhập - Hạ thế</t>
+        </is>
+      </c>
+      <c r="E14" s="38" t="n">
+        <v>-1403956</v>
+      </c>
+      <c r="F14" s="39">
+        <f>E14*80.79%</f>
+        <v/>
+      </c>
+      <c r="G14" s="39">
+        <f>E14-F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="16" t="n"/>
+    </row>
+    <row r="15" customFormat="1" s="11">
+      <c r="A15" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>VTAD2606002 - Sửa chữa lớn FCO, LA năm 2026</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="E15" s="38" t="n">
+        <v>368361493</v>
+      </c>
+      <c r="F15" s="39">
+        <f>E15*80.79%</f>
+        <v/>
+      </c>
+      <c r="G15" s="39">
+        <f>E15-F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="20" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="n"/>
+      <c r="B16" s="40" t="n"/>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="E16" s="38" t="n">
+        <v>186050850</v>
+      </c>
+      <c r="F16" s="39">
+        <f>E16*80.79%</f>
+        <v/>
+      </c>
+      <c r="G16" s="39">
+        <f>E16-F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="n"/>
+      <c r="B17" s="40" t="n"/>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Hoàn nhập - Chưa phân loại</t>
+        </is>
+      </c>
+      <c r="E17" s="38" t="n">
+        <v>-130465000</v>
+      </c>
+      <c r="F17" s="39">
+        <f>E17*80.79%</f>
+        <v/>
+      </c>
+      <c r="G17" s="39">
+        <f>E17-F17</f>
+        <v/>
+      </c>
+      <c r="H17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>VTAD2608001 - Sửa chữa lớn Công xa năm 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2608001</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="39">
+        <f>E18*80.79%</f>
+        <v/>
+      </c>
+      <c r="G18" s="39">
+        <f>E18-F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="20" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="40" t="n"/>
+      <c r="B19" s="40" t="n"/>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2608001</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="E19" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="39">
+        <f>E19*80.79%</f>
+        <v/>
+      </c>
+      <c r="G19" s="39">
+        <f>E19-F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="16" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="n"/>
+      <c r="B20" s="40" t="n"/>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>VTAD2608001</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>Hoàn nhập - Chưa phân loại</t>
+        </is>
+      </c>
+      <c r="E20" s="38" t="n">
+        <v>-580305556</v>
+      </c>
+      <c r="F20" s="39">
+        <f>E20*80.79%</f>
+        <v/>
+      </c>
+      <c r="G20" s="39">
+        <f>E20-F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="16" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="n"/>
+      <c r="C21" s="42" t="n"/>
+      <c r="D21" s="43" t="n"/>
+      <c r="E21" s="44">
+        <f>SUM(E12:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="44">
+        <f>SUM(F12:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="44">
+        <f>SUM(G12:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A18:A20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>